--- a/IG_LGC_config/ig/StructureDefinition-EyeColor.xlsx
+++ b/IG_LGC_config/ig/StructureDefinition-EyeColor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:57:24+00:00</t>
+    <t>2026-06-25T10:01:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,7 +341,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/EyeColorVS|1.0.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/EyeColorVS|0.1.0</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
